--- a/Experiments/qa_sets/human_validation/human_validation.xlsx
+++ b/Experiments/qa_sets/human_validation/human_validation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\qe\triad\qa_sets\human_validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\qe\triad\Experiments\qa_sets\human_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47195C16-FF46-4E73-89DA-14C4E421CA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18ACF08-67D4-4F5F-989D-D468C00E9456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1536" windowWidth="23232" windowHeight="11232" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36525" yWindow="7155" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HotPotQuestion Evalaution" sheetId="2" r:id="rId1"/>
@@ -38,16 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>answerbility</t>
   </si>
   <si>
     <t>Average Score:</t>
-  </si>
-  <si>
-    <t>How likely is the query
- created by an actual user?</t>
   </si>
   <si>
     <t>Is the answer to the query
@@ -62,9 +58,6 @@
     <t>correctness</t>
   </si>
   <si>
-    <t>plausibility 1-5</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -73,9 +66,6 @@
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Plausibility</t>
   </si>
   <si>
     <t>true mulithop</t>
@@ -161,11 +151,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED477142-CC8E-4E89-AC74-08F0087626AB}" name="Tabelle1377" displayName="Tabelle1377" ref="A1:F101" totalsRowShown="0">
-  <autoFilter ref="A1:F101" xr:uid="{ED477142-CC8E-4E89-AC74-08F0087626AB}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED477142-CC8E-4E89-AC74-08F0087626AB}" name="Tabelle1377" displayName="Tabelle1377" ref="A1:E101" totalsRowShown="0">
+  <autoFilter ref="A1:E101" xr:uid="{ED477142-CC8E-4E89-AC74-08F0087626AB}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{5184FCEC-E771-4F8D-80A9-D1CBA48DF03E}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{61FA871D-6178-4897-A17D-0FDBC5E10F91}" name="Plausibility"/>
     <tableColumn id="3" xr3:uid="{EF125739-1D7B-40AB-A933-7681B3A86418}" name="answerbility"/>
     <tableColumn id="5" xr3:uid="{C529E746-E54E-466C-A6CC-B6A25F319E28}" name="correctness"/>
     <tableColumn id="6" xr3:uid="{E2F6DE2B-8C14-4E50-9F93-74CAE5E106B7}" name="true mulithop"/>
@@ -176,11 +165,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3B5E1F53-03EF-4386-A8A9-FFD19FCBAA4E}" name="Tabelle137" displayName="Tabelle137" ref="A1:F101" totalsRowShown="0">
-  <autoFilter ref="A1:F101" xr:uid="{3B5E1F53-03EF-4386-A8A9-FFD19FCBAA4E}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3B5E1F53-03EF-4386-A8A9-FFD19FCBAA4E}" name="Tabelle137" displayName="Tabelle137" ref="A1:E101" totalsRowShown="0">
+  <autoFilter ref="A1:E101" xr:uid="{3B5E1F53-03EF-4386-A8A9-FFD19FCBAA4E}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F038DAE9-372A-4E72-B8ED-064F9B812EBF}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{7C43D790-6DD1-4AC4-9DBD-A4A3337B5CE9}" name="Plausibility"/>
     <tableColumn id="3" xr3:uid="{E39F8A66-24E6-4EC9-805E-94DE79FCB8B4}" name="answerbility"/>
     <tableColumn id="5" xr3:uid="{F5F4707A-BEEA-4E21-9166-087BEB8AA761}" name="correctness"/>
     <tableColumn id="6" xr3:uid="{2D3A8ACE-4F9A-4A4D-B167-FE45FBB3FDCA}" name="true mulithop"/>
@@ -465,83 +453,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12110B8C-4523-447B-8B0C-591638E7F2F1}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="8" max="8" width="63.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" customWidth="1"/>
-    <col min="10" max="10" width="30.44140625" customWidth="1"/>
-    <col min="11" max="11" width="21.5546875" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" customWidth="1"/>
-    <col min="13" max="13" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
+    <col min="7" max="7" width="63.6640625" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="30.44140625" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -552,9 +530,7 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
         <v>2</v>
       </c>
@@ -562,21 +538,18 @@
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -587,39 +560,32 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" t="s">
         <v>1</v>
       </c>
       <c r="I4">
-        <f>AVERAGE(Tabelle1377[Plausibility])</f>
-        <v>3.91</v>
-      </c>
-      <c r="J4">
         <f>AVERAGE(Tabelle1377[answerbility])</f>
         <v>0.9</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <f>AVERAGE(Tabelle1377[correctness])</f>
         <v>0.92</v>
       </c>
-      <c r="L4">
+      <c r="K4">
         <f>AVERAGE(Tabelle1377[true mulithop])</f>
         <v>0.91</v>
       </c>
-      <c r="M4">
-        <f>AVERAGE(M10,Tabelle1377[[#All],[unambiguos]])</f>
+      <c r="L4">
+        <f>AVERAGE(L10,Tabelle1377[[#All],[unambiguos]])</f>
         <v>0.92</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -630,36 +596,30 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -670,16 +630,13 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -690,16 +647,13 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -710,16 +664,13 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -730,19 +681,16 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -750,36 +698,30 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -790,16 +732,13 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -810,16 +749,13 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -830,16 +766,13 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -850,36 +783,30 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -890,16 +817,13 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -910,16 +834,13 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -930,16 +851,13 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -950,19 +868,16 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -970,16 +885,13 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -990,16 +902,13 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1010,16 +919,13 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1030,16 +936,13 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1050,16 +953,13 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1068,18 +968,15 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1088,13 +985,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1102,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1110,16 +1004,13 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1130,36 +1021,30 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1170,16 +1055,13 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1190,16 +1072,13 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1210,16 +1089,13 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1230,16 +1106,13 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1250,16 +1123,13 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1270,16 +1140,13 @@
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1290,16 +1157,13 @@
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1310,16 +1174,13 @@
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1330,16 +1191,13 @@
       <c r="E40">
         <v>1</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1350,16 +1208,13 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1368,13 +1223,10 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1390,16 +1242,13 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1408,18 +1257,15 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1430,16 +1276,13 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1450,16 +1293,13 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1470,16 +1310,13 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1490,16 +1327,13 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1510,16 +1344,13 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1530,16 +1361,13 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1550,36 +1378,30 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1590,16 +1412,13 @@
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1610,16 +1429,13 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1630,16 +1446,13 @@
       <c r="E55">
         <v>1</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1650,16 +1463,13 @@
       <c r="E56">
         <v>1</v>
       </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1668,18 +1478,15 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1690,16 +1497,13 @@
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1710,16 +1514,13 @@
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1730,16 +1531,13 @@
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1750,16 +1548,13 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1770,16 +1565,13 @@
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1790,16 +1582,13 @@
       <c r="E63">
         <v>1</v>
       </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1810,16 +1599,13 @@
       <c r="E64">
         <v>1</v>
       </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -1830,16 +1616,13 @@
       <c r="E65">
         <v>1</v>
       </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -1850,16 +1633,13 @@
       <c r="E66">
         <v>1</v>
       </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -1870,16 +1650,13 @@
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -1890,16 +1667,13 @@
       <c r="E68">
         <v>1</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -1910,16 +1684,13 @@
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -1930,11 +1701,8 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1945,41 +1713,35 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -1990,16 +1752,13 @@
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -2010,16 +1769,13 @@
       <c r="E74">
         <v>1</v>
       </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -2030,36 +1786,30 @@
       <c r="E75">
         <v>1</v>
       </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -2068,18 +1818,15 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>1</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -2090,16 +1837,13 @@
       <c r="E78">
         <v>1</v>
       </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -2110,19 +1854,16 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2130,56 +1871,47 @@
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -2190,16 +1922,13 @@
       <c r="E83">
         <v>1</v>
       </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -2210,16 +1939,13 @@
       <c r="E84">
         <v>1</v>
       </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -2230,16 +1956,13 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -2250,16 +1973,13 @@
       <c r="E86">
         <v>1</v>
       </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -2270,16 +1990,13 @@
       <c r="E87">
         <v>1</v>
       </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2290,16 +2007,13 @@
       <c r="E88">
         <v>1</v>
       </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -2310,36 +2024,30 @@
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2348,38 +2056,32 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -2390,16 +2092,13 @@
       <c r="E93">
         <v>1</v>
       </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2410,16 +2109,13 @@
       <c r="E94">
         <v>1</v>
       </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2430,16 +2126,13 @@
       <c r="E95">
         <v>1</v>
       </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -2450,16 +2143,13 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -2470,16 +2160,13 @@
       <c r="E97">
         <v>1</v>
       </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2490,36 +2177,30 @@
       <c r="E98">
         <v>1</v>
       </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -2530,16 +2211,13 @@
       <c r="E100">
         <v>1</v>
       </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -2548,9 +2226,6 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101">
         <v>0</v>
       </c>
     </row>
@@ -2564,83 +2239,73 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7780A93-5E4D-4FF3-A155-CE77D6684C13}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="8" max="8" width="63.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" customWidth="1"/>
-    <col min="10" max="10" width="30.44140625" customWidth="1"/>
-    <col min="11" max="11" width="21.5546875" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" customWidth="1"/>
-    <col min="13" max="13" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
+    <col min="7" max="7" width="63.6640625" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="30.44140625" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2651,9 +2316,7 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2661,16 +2324,13 @@
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2681,44 +2341,37 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>1</v>
       </c>
       <c r="I4">
-        <f>AVERAGE(Tabelle137[Plausibility])</f>
-        <v>3.69</v>
-      </c>
-      <c r="J4">
         <f>AVERAGE(Tabelle137[answerbility])</f>
         <v>0.93</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <f>AVERAGE(Tabelle137[correctness])</f>
         <v>0.98</v>
       </c>
-      <c r="L4">
+      <c r="K4">
         <f>AVERAGE(Tabelle137[true mulithop])</f>
         <v>0.85</v>
       </c>
-      <c r="M4">
-        <f>AVERAGE(M10,Tabelle137[[#All],[unambiguos]])</f>
+      <c r="L4">
+        <f>AVERAGE(L10,Tabelle137[[#All],[unambiguos]])</f>
         <v>0.92</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2729,16 +2382,13 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2749,36 +2399,30 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2789,36 +2433,30 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2829,16 +2467,13 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2849,16 +2484,13 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2869,19 +2501,16 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2889,16 +2518,13 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2909,36 +2535,30 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2949,16 +2569,13 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2969,36 +2586,30 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -3009,16 +2620,13 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3029,16 +2637,13 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -3049,11 +2654,8 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3061,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3069,16 +2671,13 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3089,16 +2688,13 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -3109,16 +2705,13 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -3129,36 +2722,30 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -3169,16 +2756,13 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -3189,16 +2773,13 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3209,16 +2790,13 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3229,16 +2807,13 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -3249,16 +2824,13 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -3269,11 +2841,8 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3289,16 +2858,13 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3309,16 +2875,13 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -3329,16 +2892,13 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3349,16 +2909,13 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -3369,16 +2926,13 @@
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3389,16 +2943,13 @@
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3409,16 +2960,13 @@
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3427,18 +2975,15 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -3449,16 +2994,13 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3469,16 +3011,13 @@
       <c r="E42">
         <v>1</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3489,16 +3028,13 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3509,16 +3045,13 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -3529,16 +3062,13 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -3549,16 +3079,13 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -3569,16 +3096,13 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -3589,19 +3113,16 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3609,16 +3130,13 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -3629,16 +3147,13 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -3649,16 +3164,13 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -3669,16 +3181,13 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3689,16 +3198,13 @@
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -3709,16 +3215,13 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3727,58 +3230,49 @@
         <v>1</v>
       </c>
       <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -3789,16 +3283,13 @@
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3809,16 +3300,13 @@
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -3829,16 +3317,13 @@
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3847,18 +3332,15 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3869,16 +3351,13 @@
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3889,16 +3368,13 @@
       <c r="E63">
         <v>1</v>
       </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -3909,56 +3385,47 @@
       <c r="E64">
         <v>1</v>
       </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3969,16 +3436,13 @@
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3987,18 +3451,15 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -4009,16 +3470,13 @@
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -4029,36 +3487,30 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -4067,18 +3519,15 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -4089,16 +3538,13 @@
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -4107,18 +3553,15 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -4129,16 +3572,13 @@
       <c r="E75">
         <v>1</v>
       </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -4149,16 +3589,13 @@
       <c r="E76">
         <v>1</v>
       </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -4169,16 +3606,13 @@
       <c r="E77">
         <v>1</v>
       </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -4187,18 +3621,15 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -4209,16 +3640,13 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -4229,16 +3657,13 @@
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -4249,11 +3674,8 @@
       <c r="E81">
         <v>1</v>
       </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4269,16 +3691,13 @@
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -4289,11 +3708,8 @@
       <c r="E83">
         <v>1</v>
       </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4309,76 +3725,64 @@
       <c r="E84">
         <v>1</v>
       </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -4389,16 +3793,13 @@
       <c r="E88">
         <v>1</v>
       </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -4409,16 +3810,13 @@
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -4429,16 +3827,13 @@
       <c r="E90">
         <v>1</v>
       </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -4447,18 +3842,15 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -4469,19 +3861,16 @@
       <c r="E92">
         <v>1</v>
       </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4489,16 +3878,13 @@
       <c r="E93">
         <v>1</v>
       </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -4509,36 +3895,30 @@
       <c r="E94">
         <v>1</v>
       </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>1</v>
       </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -4549,16 +3929,13 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -4569,16 +3946,13 @@
       <c r="E97">
         <v>1</v>
       </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -4589,31 +3963,25 @@
       <c r="E98">
         <v>1</v>
       </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4624,21 +3992,18 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4647,9 +4012,6 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101">
         <v>1</v>
       </c>
     </row>
@@ -4679,13 +4041,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -4699,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
